--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_CardReder_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_CardReder_240626.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DE06B3-5146-4A14-8563-BF265EC2B318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF6F648-5FE5-4770-962E-27506E7B5722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">NhapKho_SX!$A$1:$M$20</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>STT</t>
   </si>
@@ -119,6 +120,9 @@
   <si>
     <t>Nhập kho 
 thành phẩm</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -129,7 +133,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -236,8 +240,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,6 +256,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,7 +439,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -526,6 +541,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1011,66 +1035,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="48" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="50"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="51" t="s">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="51" t="s">
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="53" t="s">
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="57"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1317,4 +1341,826 @@
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9472F812-92D7-45AE-B952-AE7015ED63E9}">
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="36" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="37">
+        <v>1</v>
+      </c>
+      <c r="B2" s="37">
+        <v>20260624001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="37">
+        <v>2</v>
+      </c>
+      <c r="B3" s="37">
+        <v>20260624002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="37">
+        <v>3</v>
+      </c>
+      <c r="B4" s="37">
+        <v>20260624003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="37">
+        <v>4</v>
+      </c>
+      <c r="B5" s="37">
+        <v>20260624004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="37">
+        <v>5</v>
+      </c>
+      <c r="B6" s="37">
+        <v>20260624005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="37">
+        <v>6</v>
+      </c>
+      <c r="B7" s="37">
+        <v>20260624006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="37">
+        <v>7</v>
+      </c>
+      <c r="B8" s="37">
+        <v>20260624007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="37">
+        <v>8</v>
+      </c>
+      <c r="B9" s="37">
+        <v>20260624008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="37">
+        <v>9</v>
+      </c>
+      <c r="B10" s="37">
+        <v>20260624009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="37">
+        <v>10</v>
+      </c>
+      <c r="B11" s="37">
+        <v>20260624010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="37">
+        <v>11</v>
+      </c>
+      <c r="B12" s="37">
+        <v>20260624011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="37">
+        <v>12</v>
+      </c>
+      <c r="B13" s="37">
+        <v>20260624012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="37">
+        <v>13</v>
+      </c>
+      <c r="B14" s="37">
+        <v>20260624013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="37">
+        <v>14</v>
+      </c>
+      <c r="B15" s="37">
+        <v>20260624014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="37">
+        <v>15</v>
+      </c>
+      <c r="B16" s="37">
+        <v>20260624015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="37">
+        <v>16</v>
+      </c>
+      <c r="B17" s="37">
+        <v>20260624016</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="37">
+        <v>17</v>
+      </c>
+      <c r="B18" s="37">
+        <v>20260624017</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="37">
+        <v>18</v>
+      </c>
+      <c r="B19" s="37">
+        <v>20260624018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="37">
+        <v>19</v>
+      </c>
+      <c r="B20" s="37">
+        <v>20260624019</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="37">
+        <v>20</v>
+      </c>
+      <c r="B21" s="37">
+        <v>20260624020</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="37">
+        <v>21</v>
+      </c>
+      <c r="B22" s="37">
+        <v>20260624021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="37">
+        <v>22</v>
+      </c>
+      <c r="B23" s="37">
+        <v>20260624022</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="37">
+        <v>23</v>
+      </c>
+      <c r="B24" s="37">
+        <v>20260624023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="37">
+        <v>24</v>
+      </c>
+      <c r="B25" s="37">
+        <v>20260624024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="37">
+        <v>25</v>
+      </c>
+      <c r="B26" s="37">
+        <v>20260624025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="37">
+        <v>26</v>
+      </c>
+      <c r="B27" s="37">
+        <v>20260624026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="37">
+        <v>27</v>
+      </c>
+      <c r="B28" s="37">
+        <v>20260624027</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="37">
+        <v>28</v>
+      </c>
+      <c r="B29" s="37">
+        <v>20260624028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="37">
+        <v>29</v>
+      </c>
+      <c r="B30" s="37">
+        <v>20260624029</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="37">
+        <v>30</v>
+      </c>
+      <c r="B31" s="37">
+        <v>20260624030</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="37">
+        <v>31</v>
+      </c>
+      <c r="B32" s="37">
+        <v>20260624031</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="37">
+        <v>32</v>
+      </c>
+      <c r="B33" s="37">
+        <v>20260624032</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="37">
+        <v>33</v>
+      </c>
+      <c r="B34" s="37">
+        <v>20260624033</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="37">
+        <v>34</v>
+      </c>
+      <c r="B35" s="37">
+        <v>20260624034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="37">
+        <v>35</v>
+      </c>
+      <c r="B36" s="37">
+        <v>20260624035</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="37">
+        <v>20260624036</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="37">
+        <v>37</v>
+      </c>
+      <c r="B38" s="37">
+        <v>20260624037</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="37">
+        <v>38</v>
+      </c>
+      <c r="B39" s="37">
+        <v>20260624038</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="37">
+        <v>39</v>
+      </c>
+      <c r="B40" s="37">
+        <v>20260624039</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="37">
+        <v>40</v>
+      </c>
+      <c r="B41" s="37">
+        <v>20260624040</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="37">
+        <v>41</v>
+      </c>
+      <c r="B42" s="37">
+        <v>20260624041</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="37">
+        <v>42</v>
+      </c>
+      <c r="B43" s="37">
+        <v>20260624042</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="37">
+        <v>43</v>
+      </c>
+      <c r="B44" s="37">
+        <v>20260624043</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="37">
+        <v>44</v>
+      </c>
+      <c r="B45" s="37">
+        <v>20260624044</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="37">
+        <v>45</v>
+      </c>
+      <c r="B46" s="37">
+        <v>20260624045</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="37">
+        <v>46</v>
+      </c>
+      <c r="B47" s="37">
+        <v>20260624046</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="37">
+        <v>47</v>
+      </c>
+      <c r="B48" s="37">
+        <v>20260624047</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="37">
+        <v>48</v>
+      </c>
+      <c r="B49" s="37">
+        <v>20260624048</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="37">
+        <v>49</v>
+      </c>
+      <c r="B50" s="37">
+        <v>20260624049</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="37">
+        <v>50</v>
+      </c>
+      <c r="B51" s="37">
+        <v>20260624050</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="37">
+        <v>51</v>
+      </c>
+      <c r="B52" s="37">
+        <v>20260624051</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="37">
+        <v>52</v>
+      </c>
+      <c r="B53" s="37">
+        <v>20260624052</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="37">
+        <v>53</v>
+      </c>
+      <c r="B54" s="37">
+        <v>20260624053</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="37">
+        <v>54</v>
+      </c>
+      <c r="B55" s="37">
+        <v>20260624054</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="37">
+        <v>55</v>
+      </c>
+      <c r="B56" s="37">
+        <v>20260624055</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="37">
+        <v>56</v>
+      </c>
+      <c r="B57" s="37">
+        <v>20260624056</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="37">
+        <v>57</v>
+      </c>
+      <c r="B58" s="37">
+        <v>20260624057</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="37">
+        <v>58</v>
+      </c>
+      <c r="B59" s="37">
+        <v>20260624058</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="37">
+        <v>59</v>
+      </c>
+      <c r="B60" s="37">
+        <v>20260624059</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="37">
+        <v>60</v>
+      </c>
+      <c r="B61" s="37">
+        <v>20260624060</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="37">
+        <v>61</v>
+      </c>
+      <c r="B62" s="37">
+        <v>20260624061</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="37">
+        <v>62</v>
+      </c>
+      <c r="B63" s="37">
+        <v>20260624062</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="37">
+        <v>63</v>
+      </c>
+      <c r="B64" s="37">
+        <v>20260624063</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="37">
+        <v>64</v>
+      </c>
+      <c r="B65" s="37">
+        <v>20260624064</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="37">
+        <v>65</v>
+      </c>
+      <c r="B66" s="37">
+        <v>20260624065</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="37">
+        <v>66</v>
+      </c>
+      <c r="B67" s="37">
+        <v>20260624066</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="37">
+        <v>67</v>
+      </c>
+      <c r="B68" s="37">
+        <v>20260624067</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="37">
+        <v>68</v>
+      </c>
+      <c r="B69" s="37">
+        <v>20260624068</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="37">
+        <v>69</v>
+      </c>
+      <c r="B70" s="37">
+        <v>20260624069</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="37">
+        <v>70</v>
+      </c>
+      <c r="B71" s="37">
+        <v>20260624070</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="37">
+        <v>71</v>
+      </c>
+      <c r="B72" s="37">
+        <v>20260624071</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="37">
+        <v>72</v>
+      </c>
+      <c r="B73" s="37">
+        <v>20260624072</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="37">
+        <v>73</v>
+      </c>
+      <c r="B74" s="37">
+        <v>20260624073</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="37">
+        <v>74</v>
+      </c>
+      <c r="B75" s="37">
+        <v>20260624074</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="37">
+        <v>75</v>
+      </c>
+      <c r="B76" s="37">
+        <v>20260624075</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="37">
+        <v>76</v>
+      </c>
+      <c r="B77" s="37">
+        <v>20260624076</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="37">
+        <v>77</v>
+      </c>
+      <c r="B78" s="37">
+        <v>20260624077</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="37">
+        <v>78</v>
+      </c>
+      <c r="B79" s="37">
+        <v>20260624078</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="37">
+        <v>79</v>
+      </c>
+      <c r="B80" s="37">
+        <v>20260624079</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="37">
+        <v>80</v>
+      </c>
+      <c r="B81" s="37">
+        <v>20260624080</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="37">
+        <v>81</v>
+      </c>
+      <c r="B82" s="37">
+        <v>20260624081</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="37">
+        <v>82</v>
+      </c>
+      <c r="B83" s="37">
+        <v>20260624082</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="37">
+        <v>83</v>
+      </c>
+      <c r="B84" s="37">
+        <v>20260624083</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="37">
+        <v>84</v>
+      </c>
+      <c r="B85" s="37">
+        <v>20260624084</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="37">
+        <v>85</v>
+      </c>
+      <c r="B86" s="37">
+        <v>20260624085</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="37">
+        <v>86</v>
+      </c>
+      <c r="B87" s="37">
+        <v>20260624086</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="37">
+        <v>87</v>
+      </c>
+      <c r="B88" s="37">
+        <v>20260624087</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="37">
+        <v>88</v>
+      </c>
+      <c r="B89" s="37">
+        <v>20260624088</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="37">
+        <v>89</v>
+      </c>
+      <c r="B90" s="37">
+        <v>20260624089</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="37">
+        <v>90</v>
+      </c>
+      <c r="B91" s="37">
+        <v>20260624090</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="37">
+        <v>91</v>
+      </c>
+      <c r="B92" s="37">
+        <v>20260624091</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="37">
+        <v>92</v>
+      </c>
+      <c r="B93" s="37">
+        <v>20260624092</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="37">
+        <v>93</v>
+      </c>
+      <c r="B94" s="37">
+        <v>20260624093</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="37">
+        <v>94</v>
+      </c>
+      <c r="B95" s="37">
+        <v>20260624094</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="37">
+        <v>95</v>
+      </c>
+      <c r="B96" s="37">
+        <v>20260624095</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="37">
+        <v>96</v>
+      </c>
+      <c r="B97" s="37">
+        <v>20260624096</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="37">
+        <v>97</v>
+      </c>
+      <c r="B98" s="37">
+        <v>20260624097</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="37">
+        <v>98</v>
+      </c>
+      <c r="B99" s="37">
+        <v>20260624098</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="37">
+        <v>99</v>
+      </c>
+      <c r="B100" s="37">
+        <v>20260624099</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="37">
+        <v>100</v>
+      </c>
+      <c r="B101" s="37">
+        <v>20260624100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>